--- a/public/images/category/curtains/Curtains_Catalog.xlsx
+++ b/public/images/category/curtains/Curtains_Catalog.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Luxury\public\images\category\curtains\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89AE184-0299-451D-AD2F-EF905FE31CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Curtains Catalog" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Curtains Catalog" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,169 +38,167 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
-    <t xml:space="preserve">SKU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regular Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sale Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Short Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Towel fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towel fabric curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plush Toweling Weave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Length 5 ft, Width 8.6 ft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey, Blue, Cream, White, Red</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Towel Fabric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 in each color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made curtains in a soft, plush toweling texture. Eyelet header for easy hanging, finished in a warm, tactile weave that suits both classic and contemporary interiors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Malai curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malai curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velvet Weave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Black, Blue, White, Maroon, Red, Pink, Green, Grey, Light Brown, Offwhite, Light Grey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made velvet-finish curtains with a rich, soft pile and smooth drape. Eyelet header design offers a premium, tactile look that elevates any living space.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Bubble curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bubble curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dobby Bubble Weave / Dot Texture, Sheer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue, Green, Grey, Pink, Orange, Sky Blue, Brown, Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made sheer curtains featuring a delicate raised dot (bubble) weave. Lightweight and airy, they filter natural light beautifully while adding subtle texture to any window setting.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Moon curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moon curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Textured Matte Weave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Green, Grey, Brown, Light Grey, Dark Grey, Offwhite, Brown, Orange, Cyan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made curtains in a soft matte textured weave, offering a clean and understated look with a smooth, natural drape suited to modern interiors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-New Parday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Parday curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linen-Weave Textured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cream, White, Beige, Green, Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made curtains in a classic linen-textured weave, offering a clean, versatile look with a soft natural drape, perfect for both contemporary and traditional interiors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Palachi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palachi curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chevron Jacquard, Botanical Leaf Jacquard, Plain Sheer, Dotted Stripe Sheer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pink, Grey, Silver, White, Offwhite, Purple</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made curtains in a refined jacquard or sheer weave, offering subtle textured elegance in soft ivory tones, a versatile choice for light, airy interiors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curtains-Net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Net curtains</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linen-Weave Textured Sea through</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grey, White, Offwhite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine-made curtains in a natural linen-look weave, offering a soft textured finish that brings warmth and light-filtering elegance to any room.</t>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Regular Price</t>
+  </si>
+  <si>
+    <t>Discount %</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Short Description</t>
+  </si>
+  <si>
+    <t>Curtains-Towel fabric</t>
+  </si>
+  <si>
+    <t>Towel fabric curtains</t>
+  </si>
+  <si>
+    <t>Curtains</t>
+  </si>
+  <si>
+    <t>Plush Toweling Weave</t>
+  </si>
+  <si>
+    <t>Length 5 ft, Width 8.6 ft</t>
+  </si>
+  <si>
+    <t>Grey, Blue, Cream, White, Red</t>
+  </si>
+  <si>
+    <t>Towel Fabric</t>
+  </si>
+  <si>
+    <t>20 in each color</t>
+  </si>
+  <si>
+    <t>Machine-made curtains in a soft, plush toweling texture. Eyelet header for easy hanging, finished in a warm, tactile weave that suits both classic and contemporary interiors.</t>
+  </si>
+  <si>
+    <t>Curtains-Malai curtains</t>
+  </si>
+  <si>
+    <t>Malai curtains</t>
+  </si>
+  <si>
+    <t>Velvet Weave</t>
+  </si>
+  <si>
+    <t>Black, Blue, White, Maroon, Red, Pink, Green, Grey, Light Brown, Offwhite, Light Grey</t>
+  </si>
+  <si>
+    <t>Machine-made velvet-finish curtains with a rich, soft pile and smooth drape. Eyelet header design offers a premium, tactile look that elevates any living space.</t>
+  </si>
+  <si>
+    <t>Curtains-Bubble curtains</t>
+  </si>
+  <si>
+    <t>Bubble curtains</t>
+  </si>
+  <si>
+    <t>Dobby Bubble Weave / Dot Texture, Sheer</t>
+  </si>
+  <si>
+    <t>Blue, Green, Grey, Pink, Orange, Sky Blue, Brown, Purple</t>
+  </si>
+  <si>
+    <t>Machine-made sheer curtains featuring a delicate raised dot (bubble) weave. Lightweight and airy, they filter natural light beautifully while adding subtle texture to any window setting.</t>
+  </si>
+  <si>
+    <t>Curtains-Moon curtains</t>
+  </si>
+  <si>
+    <t>Moon curtains</t>
+  </si>
+  <si>
+    <t>Textured Matte Weave</t>
+  </si>
+  <si>
+    <t>Green, Grey, Brown, Light Grey, Dark Grey, Offwhite, Brown, Orange, Cyan</t>
+  </si>
+  <si>
+    <t>Machine-made curtains in a soft matte textured weave, offering a clean and understated look with a smooth, natural drape suited to modern interiors.</t>
+  </si>
+  <si>
+    <t>Curtains-New Parday</t>
+  </si>
+  <si>
+    <t>New Parday curtains</t>
+  </si>
+  <si>
+    <t>Linen-Weave Textured</t>
+  </si>
+  <si>
+    <t>Cream, White, Beige, Green, Silver</t>
+  </si>
+  <si>
+    <t>Machine-made curtains in a classic linen-textured weave, offering a clean, versatile look with a soft natural drape, perfect for both contemporary and traditional interiors.</t>
+  </si>
+  <si>
+    <t>Curtains-Palachi</t>
+  </si>
+  <si>
+    <t>Palachi curtains</t>
+  </si>
+  <si>
+    <t>Chevron Jacquard, Botanical Leaf Jacquard, Plain Sheer, Dotted Stripe Sheer</t>
+  </si>
+  <si>
+    <t>Pink, Grey, Silver, White, Offwhite, Purple</t>
+  </si>
+  <si>
+    <t>Machine-made curtains in a refined jacquard or sheer weave, offering subtle textured elegance in soft ivory tones, a versatile choice for light, airy interiors.</t>
+  </si>
+  <si>
+    <t>Curtains-Net</t>
+  </si>
+  <si>
+    <t>Net curtains</t>
+  </si>
+  <si>
+    <t>Linen-Weave Textured Sea through</t>
+  </si>
+  <si>
+    <t>Grey, White, Offwhite</t>
+  </si>
+  <si>
+    <t>Machine-made curtains in a natural linen-look weave, offering a soft textured finish that brings warmth and light-filtering elegance to any room.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -193,32 +207,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -237,14 +234,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFB7B7B7"/>
       </left>
@@ -260,61 +257,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -373,34 +338,362 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="45"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -438,7 +731,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
@@ -460,14 +753,14 @@
       <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="3">
         <v>2800</v>
       </c>
-      <c r="I2" s="4" t="n">
-        <f aca="false">IFERROR((H2-J2)/H2,0)</f>
-        <v>0.107142857142857</v>
-      </c>
-      <c r="J2" s="3" t="n">
+      <c r="I2" s="4">
+        <f t="shared" ref="I2:I8" si="0">IFERROR((H2-J2)/H2,0)</f>
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="J2" s="3">
         <v>2500</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -477,7 +770,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -499,14 +792,14 @@
       <c r="G3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="3">
         <v>2400</v>
       </c>
-      <c r="I3" s="4" t="n">
-        <f aca="false">IFERROR((H3-J3)/H3,0)</f>
+      <c r="I3" s="4">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="3">
         <v>1800</v>
       </c>
       <c r="K3" s="2" t="s">
@@ -516,7 +809,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -538,14 +831,14 @@
       <c r="G4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="3">
         <v>2200</v>
       </c>
-      <c r="I4" s="4" t="n">
-        <f aca="false">IFERROR((H4-J4)/H4,0)</f>
+      <c r="I4" s="4">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="3">
         <v>1650</v>
       </c>
       <c r="K4" s="2" t="s">
@@ -555,7 +848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>31</v>
       </c>
@@ -577,14 +870,14 @@
       <c r="G5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3">
         <v>2200</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <f aca="false">IFERROR((H5-J5)/H5,0)</f>
+      <c r="I5" s="4">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="3">
         <v>1650</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -594,7 +887,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -616,14 +909,14 @@
       <c r="G6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="3">
         <v>3200</v>
       </c>
-      <c r="I6" s="4" t="n">
-        <f aca="false">IFERROR((H6-J6)/H6,0)</f>
+      <c r="I6" s="4">
+        <f t="shared" si="0"/>
         <v>0.21875</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="3">
         <v>2500</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -633,7 +926,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:12" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>41</v>
       </c>
@@ -655,14 +948,14 @@
       <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="3">
         <v>2400</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <f aca="false">IFERROR((H7-J7)/H7,0)</f>
+      <c r="I7" s="4">
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="3">
         <v>1800</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -672,7 +965,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
@@ -694,14 +987,14 @@
       <c r="G8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="3">
         <v>1800</v>
       </c>
-      <c r="I8" s="4" t="n">
-        <f aca="false">IFERROR((H8-J8)/H8,0)</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="J8" s="3" t="n">
+      <c r="I8" s="4">
+        <f t="shared" si="0"/>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="J8" s="3">
         <v>1500</v>
       </c>
       <c r="K8" s="2" t="s">
@@ -712,12 +1005,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>